--- a/data/students_EXE101_12.xlsx
+++ b/data/students_EXE101_12.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">DE20102</t>
   </si>
   <si>
-    <t xml:space="preserve">khôide20102@fpt.edu.vn</t>
+    <t xml:space="preserve">khoide20102@fpt.edu.vn</t>
   </si>
   <si>
     <t xml:space="preserve">Võ Quân Khôi</t>
@@ -106,7 +106,7 @@
     <t xml:space="preserve">DE20108</t>
   </si>
   <si>
-    <t xml:space="preserve">phúcde20108@fpt.edu.vn</t>
+    <t xml:space="preserve">phucde20108@fpt.edu.vn</t>
   </si>
   <si>
     <t xml:space="preserve">Hoàng Phúc Phúc</t>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">DA20109</t>
   </si>
   <si>
-    <t xml:space="preserve">bảoda20109@fpt.edu.vn</t>
+    <t xml:space="preserve">baoda20109@fpt.edu.vn</t>
   </si>
   <si>
     <t xml:space="preserve">Phạm Huy Bảo</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">DE20110</t>
   </si>
   <si>
-    <t xml:space="preserve">quânde20110@fpt.edu.vn</t>
+    <t xml:space="preserve">quande20110@fpt.edu.vn</t>
   </si>
   <si>
     <t xml:space="preserve">Trần Huy Quân</t>
@@ -142,7 +142,7 @@
     <t xml:space="preserve">DE20112</t>
   </si>
   <si>
-    <t xml:space="preserve">đạtde20112@fpt.edu.vn</t>
+    <t xml:space="preserve">datde20112@fpt.edu.vn</t>
   </si>
   <si>
     <t xml:space="preserve">Huỳnh Long Đạt</t>
@@ -169,7 +169,7 @@
     <t xml:space="preserve">DS20115</t>
   </si>
   <si>
-    <t xml:space="preserve">khôids20115@fpt.edu.vn</t>
+    <t xml:space="preserve">khoids20115@fpt.edu.vn</t>
   </si>
   <si>
     <t xml:space="preserve">Đặng Khôi Khôi</t>
@@ -178,7 +178,7 @@
     <t xml:space="preserve">DE20116</t>
   </si>
   <si>
-    <t xml:space="preserve">bảode20116@fpt.edu.vn</t>
+    <t xml:space="preserve">baode20116@fpt.edu.vn</t>
   </si>
   <si>
     <t xml:space="preserve">Lê Khang Bảo</t>
@@ -205,7 +205,7 @@
     <t xml:space="preserve">DS20119</t>
   </si>
   <si>
-    <t xml:space="preserve">đạtds20119@fpt.edu.vn</t>
+    <t xml:space="preserve">datds20119@fpt.edu.vn</t>
   </si>
   <si>
     <t xml:space="preserve">Lê Long Đạt</t>
@@ -293,8 +293,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -493,363 +497,364 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="0" t="s">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="0" t="s">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="0" t="s">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="0" t="s">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="0" t="s">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="0" t="s">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="0" t="s">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="0" t="s">
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="0" t="s">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="0" t="s">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="0" t="s">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="0" t="s">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="0" t="s">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="0" t="s">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="0" t="s">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>65</v>
       </c>
     </row>
